--- a/margin_src/input/Nexlev/NexLev Master Sheet.xlsx
+++ b/margin_src/input/Nexlev/NexLev Master Sheet.xlsx
@@ -1307,7 +1307,7 @@
         <v>0</v>
       </c>
       <c r="AE3" s="8" t="n">
-        <v>4799</v>
+        <v>3998</v>
       </c>
       <c r="AF3" s="8" t="n">
         <v>9999</v>
